--- a/project_files/DA418_S1_Project_Evaluation Matrix.xlsx
+++ b/project_files/DA418_S1_Project_Evaluation Matrix.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\capstone-project-retail-tech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anitha\NIIT\Capstone Project\capstone-project-retail-tech\project_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC96AF0-F525-4486-A353-35C47384E542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B758C6CE-4E24-4193-90A6-ACF1C9975D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{987E23C5-98A4-4861-859D-40122838D10E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{987E23C5-98A4-4861-859D-40122838D10E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">Remarks: </t>
   </si>
   <si>
-    <t>E-Commerce Customer Analytics: Sales, Conversion, Retension and Churn Prediction</t>
-  </si>
-  <si>
     <t>1.  Anitha R</t>
   </si>
   <si>
     <t>1.  anithar2003@gmail.com</t>
+  </si>
+  <si>
+    <t>E-Commerce Sales &amp; Customer Analysis</t>
   </si>
 </sst>
 </file>
@@ -983,14 +983,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3551A7C8-4D4F-4426-BFA1-1F001E244EF3}">
   <dimension ref="B2:E36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="115.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.109375" customWidth="1"/>
+    <col min="3" max="3" width="115.88671875" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="23" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="2:5" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:5" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="29" t="s">
         <v>1</v>
       </c>
@@ -1008,56 +1008,56 @@
       <c r="D3" s="29"/>
       <c r="E3" s="4"/>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
       <c r="D4" s="29"/>
     </row>
-    <row r="5" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="27"/>
       <c r="D5" s="27"/>
     </row>
-    <row r="6" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B6" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="31"/>
     </row>
-    <row r="7" spans="2:5" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:5" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" s="27"/>
     </row>
-    <row r="8" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="27"/>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="24" t="s">
         <v>9</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="25"/>
       <c r="C13" s="9" t="s">
         <v>11</v>
@@ -1088,7 +1088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="26"/>
       <c r="C14" s="9" t="s">
         <v>12</v>
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="2:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="24" t="s">
         <v>13</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="25"/>
       <c r="C16" s="9" t="s">
         <v>15</v>
@@ -1117,7 +1117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="26"/>
       <c r="C17" s="9" t="s">
         <v>16</v>
@@ -1126,7 +1126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="24" t="s">
         <v>17</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="25"/>
       <c r="C19" s="9" t="s">
         <v>19</v>
@@ -1146,7 +1146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="26"/>
       <c r="C20" s="9" t="s">
         <v>20</v>
@@ -1155,7 +1155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="24" t="s">
         <v>21</v>
       </c>
@@ -1164,21 +1164,21 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B22" s="25"/>
       <c r="C22" s="10" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B23" s="26"/>
       <c r="C23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B24" s="11" t="s">
         <v>25</v>
       </c>
@@ -1187,21 +1187,21 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B25" s="12"/>
       <c r="C25" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B26" s="13"/>
       <c r="C26" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
         <v>29</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B28" s="12"/>
       <c r="C28" s="8" t="s">
         <v>31</v>
@@ -1221,14 +1221,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B29" s="13"/>
       <c r="C29" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B30" s="11" t="s">
         <v>33</v>
       </c>
@@ -1237,38 +1237,38 @@
       </c>
       <c r="D30" s="7"/>
     </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B31" s="12"/>
       <c r="C31" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D31" s="7"/>
     </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B32" s="13"/>
       <c r="C32" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="7"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B33" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="16"/>
     </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B34" s="17"/>
       <c r="C34" s="18"/>
       <c r="D34" s="19"/>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B35" s="17"/>
       <c r="C35" s="18"/>
       <c r="D35" s="19"/>
     </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B36" s="20"/>
       <c r="C36" s="21"/>
       <c r="D36" s="22"/>
@@ -1300,13 +1300,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4607A829-F514-468A-8AD9-DDF51F6614C8}">
   <dimension ref="D6:E14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="59.5703125" customWidth="1"/>
+    <col min="4" max="4" width="59.5546875" customWidth="1"/>
     <col min="5" max="5" width="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D6" s="32" t="s">
         <v>25</v>
       </c>
@@ -1314,19 +1314,19 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D7" s="33"/>
       <c r="E7" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D8" s="34"/>
       <c r="E8" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D9" s="11" t="s">
         <v>29</v>
       </c>
@@ -1334,19 +1334,19 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D10" s="12"/>
       <c r="E10" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D11" s="13"/>
       <c r="E11" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D12" s="11" t="s">
         <v>33</v>
       </c>
@@ -1354,13 +1354,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D13" s="12"/>
       <c r="E13" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D14" s="13"/>
       <c r="E14" s="8" t="s">
         <v>36</v>
@@ -1377,14 +1377,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1637,21 +1635,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b18f8198-02fb-408b-a649-baf04150ea28">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0f01b7b4-d4b6-47da-93c5-cffa90a406b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCFB20A3-11D3-4F21-A3E5-84487BC2ED79}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C224B2-9B11-4DD1-9475-843BE1A9F5EF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
-    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1676,9 +1673,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C224B2-9B11-4DD1-9475-843BE1A9F5EF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCFB20A3-11D3-4F21-A3E5-84487BC2ED79}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b18f8198-02fb-408b-a649-baf04150ea28"/>
+    <ds:schemaRef ds:uri="0f01b7b4-d4b6-47da-93c5-cffa90a406b9"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>